--- a/examples/excel/cell-formatting.xlsx
+++ b/examples/excel/cell-formatting.xlsx
@@ -3,13 +3,87 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Fills" sheetId="2" r:id="R707a65820c354b06"/>
-    <x:sheet name="Borders" sheetId="3" r:id="R09b12253e7b0413d"/>
-    <x:sheet name="Numbers" sheetId="4" r:id="R0b9cc525e6664047"/>
-    <x:sheet name="Data" sheetId="5" r:id="R9ed3ab3c1eaf446f"/>
+    <x:sheet name="Fills" sheetId="2" r:id="R423637b7f6014b8d"/>
+    <x:sheet name="Borders" sheetId="3" r:id="Rbb98f24d82534ca6"/>
+    <x:sheet name="Numbers" sheetId="4" r:id="R698bfdc85f8448f5"/>
+    <x:sheet name="Data" sheetId="5" r:id="Rbf7cc62c47cb4ea8"/>
+    <x:sheet name="RichText" sheetId="6" r:id="R2321056e0a034eb5"/>
   </x:sheets>
   <x:calcPr fullCalcOnLoad="1"/>
 </x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:rPr>
+      <x:t xml:space="preserve">Bold + Red  </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:color rgb="FF2E75B6"/>
+      </x:rPr>
+      <x:t xml:space="preserve">Italic + Blue</x:t>
+    </x:r>
+    <x:r>
+      <x:t xml:space="preserve">  Normal</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="18"/>
+        <x:color rgb="FF1F4E79"/>
+      </x:rPr>
+      <x:t xml:space="preserve">H</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:vertAlign val="superscript"/>
+        <x:sz val="10"/>
+      </x:rPr>
+      <x:t xml:space="preserve">2</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:color rgb="FF1F4E79"/>
+      </x:rPr>
+      <x:t xml:space="preserve">O water formula</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:strike/>
+      </x:rPr>
+      <x:t xml:space="preserve">Strike</x:t>
+    </x:r>
+    <x:r>
+      <x:t xml:space="preserve"> | </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:u/>
+      </x:rPr>
+      <x:t xml:space="preserve">underline</x:t>
+    </x:r>
+    <x:r>
+      <x:t xml:space="preserve"> | </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="14"/>
+      </x:rPr>
+      <x:t xml:space="preserve">size 14pt</x:t>
+    </x:r>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -98,7 +172,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -173,6 +247,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF2E75B6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B2C8B"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -255,7 +334,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyFont="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="53">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyFont="1" applyFill="1"/>
@@ -334,6 +413,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyFont="1" applyFill="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -743,7 +823,37 @@
     <x:mergeCell ref="A13:C13"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="R92a4c6cdd80e4a84" tooltip="Open the repo"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="Ra6f3ae9e7270429a" tooltip="Open the repo"/>
   </x:hyperlinks>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:cols>
+    <x:col min="1" max="1" width="50" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="52" t="str">
+        <x:v>runs — rich-text within one cell</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+</x:worksheet>
 </file>